--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464956</v>
+        <v>124462807</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,38 +1478,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576386</v>
+        <v>576313</v>
       </c>
       <c r="R9" t="n">
-        <v>7056351</v>
+        <v>7056397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124461936</v>
+        <v>124465974</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,43 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576362</v>
+        <v>576547</v>
       </c>
       <c r="R10" t="n">
-        <v>7056386</v>
+        <v>7056300</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1662,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1672,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1687,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466297</v>
+        <v>124467291</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1715,21 +1721,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1739,10 +1745,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576620</v>
+        <v>576639</v>
       </c>
       <c r="R11" t="n">
-        <v>7056231</v>
+        <v>7056205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1774,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1784,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1811,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124463988</v>
+        <v>124466297</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,39 +1833,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576347</v>
+        <v>576620</v>
       </c>
       <c r="R12" t="n">
-        <v>7056490</v>
+        <v>7056231</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1891,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1901,12 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,7 +1929,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462424</v>
+        <v>124465046</v>
       </c>
       <c r="B13" t="n">
         <v>56714</v>
@@ -1978,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576338</v>
+        <v>576421</v>
       </c>
       <c r="R13" t="n">
-        <v>7056370</v>
+        <v>7056365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,22 +2034,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124461847</v>
+        <v>124464981</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>56112</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,21 +2062,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,14 +2087,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576357</v>
+        <v>576414</v>
       </c>
       <c r="R14" t="n">
-        <v>7056418</v>
+        <v>7056380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462696</v>
+        <v>124463988</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,34 +2179,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576319</v>
+        <v>576347</v>
       </c>
       <c r="R15" t="n">
-        <v>7056393</v>
+        <v>7056490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2253,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2279,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124467291</v>
+        <v>124464956</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,25 +2297,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2319,10 +2325,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576639</v>
+        <v>576386</v>
       </c>
       <c r="R16" t="n">
-        <v>7056205</v>
+        <v>7056351</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2354,7 +2360,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2364,7 +2370,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2391,10 +2397,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462807</v>
+        <v>124462526</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2407,16 +2413,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2427,7 +2433,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2436,10 +2442,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576313</v>
+        <v>576338</v>
       </c>
       <c r="R17" t="n">
-        <v>7056397</v>
+        <v>7056370</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,12 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,22 +2502,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464981</v>
+        <v>124461936</v>
       </c>
       <c r="B18" t="n">
-        <v>56112</v>
+        <v>57666</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,27 +2530,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2558,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576414</v>
+        <v>576362</v>
       </c>
       <c r="R18" t="n">
-        <v>7056380</v>
+        <v>7056386</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2618,22 +2623,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124463852</v>
+        <v>124461847</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,16 +2651,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2666,19 +2671,19 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576328</v>
+        <v>576357</v>
       </c>
       <c r="R19" t="n">
-        <v>7056469</v>
+        <v>7056418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124465974</v>
+        <v>124463852</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,16 +2768,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2788,19 +2788,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576547</v>
+        <v>576328</v>
       </c>
       <c r="R20" t="n">
-        <v>7056300</v>
+        <v>7056469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2842,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462957</v>
+        <v>124462877</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,39 +2890,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576305</v>
+        <v>576338</v>
       </c>
       <c r="R21" t="n">
-        <v>7056419</v>
+        <v>7056426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,12 +2959,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2974,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124465046</v>
+        <v>124462696</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,39 +3002,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576421</v>
+        <v>576319</v>
       </c>
       <c r="R22" t="n">
-        <v>7056365</v>
+        <v>7056393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462877</v>
+        <v>124462957</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,34 +3114,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576338</v>
+        <v>576305</v>
       </c>
       <c r="R23" t="n">
-        <v>7056426</v>
+        <v>7056419</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462807</v>
+        <v>124464956</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,43 +1478,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576313</v>
+        <v>576386</v>
       </c>
       <c r="R9" t="n">
-        <v>7056397</v>
+        <v>7056351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124465974</v>
+        <v>124467291</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,39 +1594,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576547</v>
+        <v>576639</v>
       </c>
       <c r="R10" t="n">
-        <v>7056300</v>
+        <v>7056205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1690,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467291</v>
+        <v>124463852</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,34 +1706,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576639</v>
+        <v>576328</v>
       </c>
       <c r="R11" t="n">
-        <v>7056205</v>
+        <v>7056469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466297</v>
+        <v>124462526</v>
       </c>
       <c r="B12" t="n">
-        <v>91030</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,34 +1828,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576620</v>
+        <v>576338</v>
       </c>
       <c r="R12" t="n">
-        <v>7056231</v>
+        <v>7056370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124465046</v>
+        <v>124463988</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,16 +1945,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1965,7 +1965,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576421</v>
+        <v>576347</v>
       </c>
       <c r="R13" t="n">
-        <v>7056365</v>
+        <v>7056490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2019,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464981</v>
+        <v>124462877</v>
       </c>
       <c r="B14" t="n">
-        <v>56112</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,39 +2067,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576414</v>
+        <v>576338</v>
       </c>
       <c r="R14" t="n">
-        <v>7056380</v>
+        <v>7056426</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,19 +2151,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124463988</v>
+        <v>124462807</v>
       </c>
       <c r="B15" t="n">
         <v>57513</v>
@@ -2199,7 +2199,7 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2208,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576347</v>
+        <v>576313</v>
       </c>
       <c r="R15" t="n">
-        <v>7056490</v>
+        <v>7056397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2285,10 +2285,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464956</v>
+        <v>124464981</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>56112</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2297,38 +2297,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>206004</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576386</v>
+        <v>576414</v>
       </c>
       <c r="R16" t="n">
-        <v>7056351</v>
+        <v>7056380</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2360,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2370,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2397,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462526</v>
+        <v>124465974</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,16 +2418,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2433,19 +2438,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576338</v>
+        <v>576547</v>
       </c>
       <c r="R17" t="n">
-        <v>7056370</v>
+        <v>7056300</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,22 +2507,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124461936</v>
+        <v>124466297</v>
       </c>
       <c r="B18" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,43 +2535,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576362</v>
+        <v>576620</v>
       </c>
       <c r="R18" t="n">
-        <v>7056386</v>
+        <v>7056231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2623,12 +2619,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2752,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124463852</v>
+        <v>124462696</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,39 +2764,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576328</v>
+        <v>576319</v>
       </c>
       <c r="R20" t="n">
-        <v>7056469</v>
+        <v>7056393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,12 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2874,10 +2860,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462877</v>
+        <v>124461936</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,34 +2876,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576338</v>
+        <v>576362</v>
       </c>
       <c r="R21" t="n">
-        <v>7056426</v>
+        <v>7056386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2986,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462696</v>
+        <v>124462957</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3002,34 +2997,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576319</v>
+        <v>576305</v>
       </c>
       <c r="R22" t="n">
-        <v>7056393</v>
+        <v>7056419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3071,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462957</v>
+        <v>124465046</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,16 +3119,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3134,7 +3139,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3143,10 +3148,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576305</v>
+        <v>576421</v>
       </c>
       <c r="R23" t="n">
-        <v>7056419</v>
+        <v>7056365</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464956</v>
+        <v>124463988</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,38 +1478,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576386</v>
+        <v>576347</v>
       </c>
       <c r="R9" t="n">
-        <v>7056351</v>
+        <v>7056490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467291</v>
+        <v>124462807</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576639</v>
+        <v>576313</v>
       </c>
       <c r="R10" t="n">
-        <v>7056205</v>
+        <v>7056397</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124463852</v>
+        <v>124461936</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,27 +1726,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1735,10 +1759,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576328</v>
+        <v>576362</v>
       </c>
       <c r="R11" t="n">
-        <v>7056469</v>
+        <v>7056386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1804,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,22 +1819,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462526</v>
+        <v>124462957</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,16 +1847,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,7 +1867,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1857,10 +1876,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576338</v>
+        <v>576305</v>
       </c>
       <c r="R12" t="n">
-        <v>7056370</v>
+        <v>7056419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1911,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1921,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,22 +1941,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124463988</v>
+        <v>124464981</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,27 +1969,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1974,10 +1998,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576347</v>
+        <v>576414</v>
       </c>
       <c r="R13" t="n">
-        <v>7056490</v>
+        <v>7056380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,12 +2043,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2070,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124462877</v>
+        <v>124467291</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,21 +2086,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2091,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576338</v>
+        <v>576639</v>
       </c>
       <c r="R14" t="n">
-        <v>7056426</v>
+        <v>7056205</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462807</v>
+        <v>124462877</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,39 +2198,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576313</v>
+        <v>576338</v>
       </c>
       <c r="R15" t="n">
-        <v>7056397</v>
+        <v>7056426</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,12 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,22 +2282,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464981</v>
+        <v>124461847</v>
       </c>
       <c r="B16" t="n">
-        <v>56112</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,21 +2310,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2326,14 +2335,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576414</v>
+        <v>576357</v>
       </c>
       <c r="R16" t="n">
-        <v>7056380</v>
+        <v>7056418</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,7 +2374,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2384,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124465974</v>
+        <v>124462424</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,16 +2427,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2438,19 +2447,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576547</v>
+        <v>576338</v>
       </c>
       <c r="R17" t="n">
-        <v>7056300</v>
+        <v>7056370</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2491,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2501,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2507,12 +2516,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2631,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124461847</v>
+        <v>124462696</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,39 +2656,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576357</v>
+        <v>576319</v>
       </c>
       <c r="R19" t="n">
-        <v>7056418</v>
+        <v>7056393</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462696</v>
+        <v>124465974</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,34 +2768,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576319</v>
+        <v>576547</v>
       </c>
       <c r="R20" t="n">
-        <v>7056393</v>
+        <v>7056300</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461936</v>
+        <v>124463852</v>
       </c>
       <c r="B21" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2876,31 +2885,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2909,10 +2914,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576362</v>
+        <v>576328</v>
       </c>
       <c r="R21" t="n">
-        <v>7056386</v>
+        <v>7056469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2959,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2969,22 +2979,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462957</v>
+        <v>124464956</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2993,43 +3003,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576305</v>
+        <v>576386</v>
       </c>
       <c r="R22" t="n">
-        <v>7056419</v>
+        <v>7056351</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3066,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,12 +3076,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124463988</v>
+        <v>124462807</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1502,7 +1502,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576347</v>
+        <v>576313</v>
       </c>
       <c r="R9" t="n">
-        <v>7056490</v>
+        <v>7056397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462807</v>
+        <v>124462877</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,39 +1604,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576313</v>
+        <v>576338</v>
       </c>
       <c r="R10" t="n">
-        <v>7056397</v>
+        <v>7056426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,22 +1688,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124461936</v>
+        <v>124467291</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,43 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576362</v>
+        <v>576639</v>
       </c>
       <c r="R11" t="n">
-        <v>7056386</v>
+        <v>7056205</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1794,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1819,22 +1800,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462957</v>
+        <v>124462696</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,39 +1828,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576305</v>
+        <v>576319</v>
       </c>
       <c r="R12" t="n">
-        <v>7056419</v>
+        <v>7056393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1911,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1921,12 +1897,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2070,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124467291</v>
+        <v>124462957</v>
       </c>
       <c r="B14" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2086,34 +2057,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576639</v>
+        <v>576305</v>
       </c>
       <c r="R14" t="n">
-        <v>7056205</v>
+        <v>7056419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2131,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462877</v>
+        <v>124461936</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2198,34 +2179,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576338</v>
+        <v>576362</v>
       </c>
       <c r="R15" t="n">
-        <v>7056426</v>
+        <v>7056386</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2257,7 +2247,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2267,7 +2257,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,7 +2284,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124461847</v>
+        <v>124462526</v>
       </c>
       <c r="B16" t="n">
         <v>56714</v>
@@ -2335,14 +2325,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576357</v>
+        <v>576338</v>
       </c>
       <c r="R16" t="n">
-        <v>7056418</v>
+        <v>7056370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2374,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2384,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,22 +2389,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462424</v>
+        <v>124464956</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>96227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2423,43 +2413,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576338</v>
+        <v>576386</v>
       </c>
       <c r="R17" t="n">
-        <v>7056370</v>
+        <v>7056351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2491,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2501,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2516,12 +2501,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2640,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462696</v>
+        <v>124463852</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2656,34 +2641,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576319</v>
+        <v>576328</v>
       </c>
       <c r="R19" t="n">
-        <v>7056393</v>
+        <v>7056469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,7 +2715,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124465974</v>
+        <v>124461847</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,16 +2763,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2788,7 +2783,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2797,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576547</v>
+        <v>576357</v>
       </c>
       <c r="R20" t="n">
-        <v>7056300</v>
+        <v>7056418</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2837,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2864,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124463852</v>
+        <v>124465046</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,16 +2880,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2905,7 +2900,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2914,10 +2909,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576328</v>
+        <v>576421</v>
       </c>
       <c r="R21" t="n">
-        <v>7056469</v>
+        <v>7056365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,12 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124464956</v>
+        <v>124463988</v>
       </c>
       <c r="B22" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,38 +2993,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576386</v>
+        <v>576347</v>
       </c>
       <c r="R22" t="n">
-        <v>7056351</v>
+        <v>7056490</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3076,7 +3071,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124465046</v>
+        <v>124465974</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,16 +3119,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3139,19 +3139,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576421</v>
+        <v>576547</v>
       </c>
       <c r="R23" t="n">
-        <v>7056365</v>
+        <v>7056300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462807</v>
+        <v>124462526</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,7 +1502,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576313</v>
+        <v>576338</v>
       </c>
       <c r="R9" t="n">
-        <v>7056397</v>
+        <v>7056370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,22 +1571,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462877</v>
+        <v>124464956</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1600,25 +1595,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1628,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576338</v>
+        <v>576386</v>
       </c>
       <c r="R10" t="n">
-        <v>7056426</v>
+        <v>7056351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,22 +1683,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124467291</v>
+        <v>124461847</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,34 +1711,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576639</v>
+        <v>576357</v>
       </c>
       <c r="R11" t="n">
-        <v>7056205</v>
+        <v>7056418</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462696</v>
+        <v>124463988</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,34 +1828,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576319</v>
+        <v>576347</v>
       </c>
       <c r="R12" t="n">
-        <v>7056393</v>
+        <v>7056490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,7 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1924,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464981</v>
+        <v>124467291</v>
       </c>
       <c r="B13" t="n">
-        <v>56112</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1940,39 +1950,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576414</v>
+        <v>576639</v>
       </c>
       <c r="R13" t="n">
-        <v>7056380</v>
+        <v>7056205</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,7 +2046,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124462957</v>
+        <v>124462807</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2086,10 +2091,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576305</v>
+        <v>576313</v>
       </c>
       <c r="R14" t="n">
-        <v>7056419</v>
+        <v>7056397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,12 +2136,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,10 +2168,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124461936</v>
+        <v>124463852</v>
       </c>
       <c r="B15" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,31 +2184,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2212,10 +2213,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576362</v>
+        <v>576328</v>
       </c>
       <c r="R15" t="n">
-        <v>7056386</v>
+        <v>7056469</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2247,7 +2248,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2257,7 +2258,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,22 +2278,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462526</v>
+        <v>124462877</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2300,29 +2306,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2332,7 +2333,7 @@
         <v>576338</v>
       </c>
       <c r="R16" t="n">
-        <v>7056370</v>
+        <v>7056426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2365,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2375,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464956</v>
+        <v>124465974</v>
       </c>
       <c r="B17" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,38 +2414,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576386</v>
+        <v>576547</v>
       </c>
       <c r="R17" t="n">
-        <v>7056351</v>
+        <v>7056300</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2482,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2492,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2625,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124463852</v>
+        <v>124464981</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2641,27 +2647,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2670,10 +2676,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576328</v>
+        <v>576414</v>
       </c>
       <c r="R19" t="n">
-        <v>7056469</v>
+        <v>7056380</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2705,7 +2711,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2715,12 +2721,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2748,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124461847</v>
+        <v>124462957</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,16 +2764,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2783,19 +2784,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576357</v>
+        <v>576305</v>
       </c>
       <c r="R20" t="n">
-        <v>7056418</v>
+        <v>7056419</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,7 +2828,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,7 +2838,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2981,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124463988</v>
+        <v>124462696</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,39 +3003,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576347</v>
+        <v>576319</v>
       </c>
       <c r="R22" t="n">
-        <v>7056490</v>
+        <v>7056393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,12 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124465974</v>
+        <v>124461936</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,39 +3115,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576547</v>
+        <v>576362</v>
       </c>
       <c r="R23" t="n">
-        <v>7056300</v>
+        <v>7056386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -2402,10 +2402,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124465974</v>
+        <v>124466297</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,39 +2418,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576547</v>
+        <v>576620</v>
       </c>
       <c r="R17" t="n">
-        <v>7056300</v>
+        <v>7056231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2482,7 +2477,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2492,7 +2487,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2519,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466297</v>
+        <v>124465974</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,34 +2530,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576620</v>
+        <v>576547</v>
       </c>
       <c r="R18" t="n">
-        <v>7056231</v>
+        <v>7056300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462526</v>
+        <v>124464956</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,43 +1478,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576338</v>
+        <v>576386</v>
       </c>
       <c r="R9" t="n">
-        <v>7056370</v>
+        <v>7056351</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,22 +1566,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464956</v>
+        <v>124462526</v>
       </c>
       <c r="B10" t="n">
-        <v>96227</v>
+        <v>56714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,38 +1590,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576386</v>
+        <v>576338</v>
       </c>
       <c r="R10" t="n">
-        <v>7056351</v>
+        <v>7056370</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,12 +1683,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2870,10 +2870,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124465046</v>
+        <v>124462696</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2886,39 +2886,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576421</v>
+        <v>576319</v>
       </c>
       <c r="R21" t="n">
-        <v>7056365</v>
+        <v>7056393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2950,7 +2945,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2960,7 +2955,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2987,10 +2982,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462696</v>
+        <v>124465046</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3003,34 +2998,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576319</v>
+        <v>576421</v>
       </c>
       <c r="R22" t="n">
-        <v>7056393</v>
+        <v>7056365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464956</v>
+        <v>124465046</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>56714</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,38 +1478,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576386</v>
+        <v>576421</v>
       </c>
       <c r="R9" t="n">
-        <v>7056351</v>
+        <v>7056365</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462526</v>
+        <v>124462877</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,29 +1599,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -1626,7 +1626,7 @@
         <v>576338</v>
       </c>
       <c r="R10" t="n">
-        <v>7056370</v>
+        <v>7056426</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124461847</v>
+        <v>124466297</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,39 +1711,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576357</v>
+        <v>576620</v>
       </c>
       <c r="R11" t="n">
-        <v>7056418</v>
+        <v>7056231</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1812,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124463988</v>
+        <v>124464956</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1824,43 +1819,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576347</v>
+        <v>576386</v>
       </c>
       <c r="R12" t="n">
-        <v>7056490</v>
+        <v>7056351</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1882,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1892,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1919,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467291</v>
+        <v>124463988</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,34 +1935,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576639</v>
+        <v>576347</v>
       </c>
       <c r="R13" t="n">
-        <v>7056205</v>
+        <v>7056490</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +1999,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2009,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124462807</v>
+        <v>124462424</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2062,16 +2057,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2082,7 +2077,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2091,10 +2086,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576313</v>
+        <v>576338</v>
       </c>
       <c r="R14" t="n">
-        <v>7056397</v>
+        <v>7056370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,12 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124463852</v>
+        <v>124465974</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2184,16 +2174,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2204,19 +2194,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576328</v>
+        <v>576547</v>
       </c>
       <c r="R15" t="n">
-        <v>7056469</v>
+        <v>7056300</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2248,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2258,12 +2248,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2290,10 +2275,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462877</v>
+        <v>124461936</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,34 +2291,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576338</v>
+        <v>576362</v>
       </c>
       <c r="R16" t="n">
-        <v>7056426</v>
+        <v>7056386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2365,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2375,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2402,10 +2396,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466297</v>
+        <v>124464981</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>56112</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,34 +2412,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>206004</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576620</v>
+        <v>576414</v>
       </c>
       <c r="R17" t="n">
-        <v>7056231</v>
+        <v>7056380</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2477,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2487,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124465974</v>
+        <v>124462696</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2530,39 +2529,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576547</v>
+        <v>576319</v>
       </c>
       <c r="R18" t="n">
-        <v>7056300</v>
+        <v>7056393</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,7 +2588,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2598,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2631,10 +2625,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124464981</v>
+        <v>124462807</v>
       </c>
       <c r="B19" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2647,27 +2641,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2676,10 +2670,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576414</v>
+        <v>576313</v>
       </c>
       <c r="R19" t="n">
-        <v>7056380</v>
+        <v>7056397</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2711,7 +2705,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2721,7 +2715,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462957</v>
+        <v>124467291</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,39 +2763,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576305</v>
+        <v>576639</v>
       </c>
       <c r="R20" t="n">
-        <v>7056419</v>
+        <v>7056205</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2828,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2838,12 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,10 +2859,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462696</v>
+        <v>124461847</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2886,34 +2875,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576319</v>
+        <v>576357</v>
       </c>
       <c r="R21" t="n">
-        <v>7056393</v>
+        <v>7056418</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2945,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2955,7 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2982,10 +2976,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124465046</v>
+        <v>124462957</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2998,16 +2992,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3018,7 +3012,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3027,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576421</v>
+        <v>576305</v>
       </c>
       <c r="R22" t="n">
-        <v>7056365</v>
+        <v>7056419</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3062,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3072,7 +3066,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3099,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124461936</v>
+        <v>124463852</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3115,31 +3114,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3148,10 +3143,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576362</v>
+        <v>576328</v>
       </c>
       <c r="R23" t="n">
-        <v>7056386</v>
+        <v>7056469</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124465046</v>
+        <v>124467291</v>
       </c>
       <c r="B9" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,39 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576421</v>
+        <v>576639</v>
       </c>
       <c r="R9" t="n">
-        <v>7056365</v>
+        <v>7056205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124462877</v>
+        <v>124464956</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,25 +1590,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1623,10 +1618,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576338</v>
+        <v>576386</v>
       </c>
       <c r="R10" t="n">
-        <v>7056426</v>
+        <v>7056351</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1653,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1663,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,22 +1678,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466297</v>
+        <v>124463852</v>
       </c>
       <c r="B11" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,34 +1706,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576620</v>
+        <v>576328</v>
       </c>
       <c r="R11" t="n">
-        <v>7056231</v>
+        <v>7056469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1780,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464956</v>
+        <v>124465974</v>
       </c>
       <c r="B12" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,38 +1824,43 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576386</v>
+        <v>576547</v>
       </c>
       <c r="R12" t="n">
-        <v>7056351</v>
+        <v>7056300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1882,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1892,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1919,10 +1929,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124463988</v>
+        <v>124462424</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1935,16 +1945,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1955,7 +1965,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1964,10 +1974,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576347</v>
+        <v>576338</v>
       </c>
       <c r="R13" t="n">
-        <v>7056490</v>
+        <v>7056370</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1999,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2009,12 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,22 +2034,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124462424</v>
+        <v>124466297</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,39 +2062,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576338</v>
+        <v>576620</v>
       </c>
       <c r="R14" t="n">
-        <v>7056370</v>
+        <v>7056231</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,22 +2146,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124465974</v>
+        <v>124462957</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576547</v>
+        <v>576305</v>
       </c>
       <c r="R15" t="n">
-        <v>7056300</v>
+        <v>7056419</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,7 +2248,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2396,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464981</v>
+        <v>124462696</v>
       </c>
       <c r="B17" t="n">
-        <v>56112</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2412,39 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576414</v>
+        <v>576319</v>
       </c>
       <c r="R17" t="n">
-        <v>7056380</v>
+        <v>7056393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2513,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124462696</v>
+        <v>124464981</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>56112</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,34 +2529,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576319</v>
+        <v>576414</v>
       </c>
       <c r="R18" t="n">
-        <v>7056393</v>
+        <v>7056380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2588,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2598,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2747,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124467291</v>
+        <v>124465046</v>
       </c>
       <c r="B20" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,34 +2768,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576639</v>
+        <v>576421</v>
       </c>
       <c r="R20" t="n">
-        <v>7056205</v>
+        <v>7056365</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461847</v>
+        <v>124462877</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,39 +2885,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576357</v>
+        <v>576338</v>
       </c>
       <c r="R21" t="n">
-        <v>7056418</v>
+        <v>7056426</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2964,19 +2969,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462957</v>
+        <v>124463988</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3012,7 +3017,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -3021,10 +3026,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576305</v>
+        <v>576347</v>
       </c>
       <c r="R22" t="n">
-        <v>7056419</v>
+        <v>7056490</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3066,12 +3071,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124463852</v>
+        <v>124461847</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,16 +3119,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3134,19 +3139,19 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576328</v>
+        <v>576357</v>
       </c>
       <c r="R23" t="n">
-        <v>7056469</v>
+        <v>7056418</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467291</v>
+        <v>124462957</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,34 +1482,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576639</v>
+        <v>576305</v>
       </c>
       <c r="R9" t="n">
-        <v>7056205</v>
+        <v>7056419</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464956</v>
+        <v>124463988</v>
       </c>
       <c r="B10" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,38 +1600,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576386</v>
+        <v>576347</v>
       </c>
       <c r="R10" t="n">
-        <v>7056351</v>
+        <v>7056490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1653,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1663,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1690,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124463852</v>
+        <v>124462877</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1706,39 +1726,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576328</v>
+        <v>576338</v>
       </c>
       <c r="R11" t="n">
-        <v>7056469</v>
+        <v>7056426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,12 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124465974</v>
+        <v>124464981</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>56112</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,39 +1838,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576547</v>
+        <v>576414</v>
       </c>
       <c r="R12" t="n">
-        <v>7056300</v>
+        <v>7056380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462424</v>
+        <v>124461936</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,27 +1955,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1974,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576338</v>
+        <v>576362</v>
       </c>
       <c r="R13" t="n">
-        <v>7056370</v>
+        <v>7056386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2023,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2033,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466297</v>
+        <v>124464956</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2058,25 +2072,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2086,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576620</v>
+        <v>576386</v>
       </c>
       <c r="R14" t="n">
-        <v>7056231</v>
+        <v>7056351</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2121,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2131,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2158,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462957</v>
+        <v>124461847</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2174,16 +2188,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2194,19 +2208,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576305</v>
+        <v>576357</v>
       </c>
       <c r="R15" t="n">
-        <v>7056419</v>
+        <v>7056418</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2238,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2248,12 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124461936</v>
+        <v>124466297</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,43 +2305,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576362</v>
+        <v>576620</v>
       </c>
       <c r="R16" t="n">
-        <v>7056386</v>
+        <v>7056231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,22 +2389,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462696</v>
+        <v>124462807</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,34 +2417,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576319</v>
+        <v>576313</v>
       </c>
       <c r="R17" t="n">
-        <v>7056393</v>
+        <v>7056397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2491,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2513,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464981</v>
+        <v>124467291</v>
       </c>
       <c r="B18" t="n">
-        <v>56112</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,39 +2539,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576414</v>
+        <v>576639</v>
       </c>
       <c r="R18" t="n">
-        <v>7056380</v>
+        <v>7056205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2630,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462807</v>
+        <v>124465046</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2646,16 +2651,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2666,7 +2671,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2675,10 +2680,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576313</v>
+        <v>576421</v>
       </c>
       <c r="R19" t="n">
-        <v>7056397</v>
+        <v>7056365</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2715,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2725,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124465046</v>
+        <v>124463852</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,16 +2768,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2788,7 +2788,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2797,10 +2797,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576421</v>
+        <v>576328</v>
       </c>
       <c r="R20" t="n">
-        <v>7056365</v>
+        <v>7056469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2842,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462877</v>
+        <v>124462424</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,24 +2890,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2912,7 +2922,7 @@
         <v>576338</v>
       </c>
       <c r="R21" t="n">
-        <v>7056426</v>
+        <v>7056370</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2954,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2964,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,10 +2991,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124463988</v>
+        <v>124462696</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,39 +3007,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576347</v>
+        <v>576319</v>
       </c>
       <c r="R22" t="n">
-        <v>7056490</v>
+        <v>7056393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3066,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,12 +3076,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124461847</v>
+        <v>124465974</v>
       </c>
       <c r="B23" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,16 +3119,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3139,7 +3139,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576357</v>
+        <v>576547</v>
       </c>
       <c r="R23" t="n">
-        <v>7056418</v>
+        <v>7056300</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1710,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124462877</v>
+        <v>124464981</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56112</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,34 +1726,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576338</v>
+        <v>576414</v>
       </c>
       <c r="R11" t="n">
-        <v>7056426</v>
+        <v>7056380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,22 +1815,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124464981</v>
+        <v>124462877</v>
       </c>
       <c r="B12" t="n">
-        <v>56112</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,39 +1843,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576414</v>
+        <v>576338</v>
       </c>
       <c r="R12" t="n">
-        <v>7056380</v>
+        <v>7056426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,12 +1927,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,7 +1466,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462957</v>
+        <v>124463852</v>
       </c>
       <c r="B9" t="n">
         <v>57513</v>
@@ -1502,7 +1502,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576305</v>
+        <v>576328</v>
       </c>
       <c r="R9" t="n">
-        <v>7056419</v>
+        <v>7056469</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124463988</v>
+        <v>124461936</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,27 +1604,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1633,10 +1637,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576347</v>
+        <v>576362</v>
       </c>
       <c r="R10" t="n">
-        <v>7056490</v>
+        <v>7056386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1672,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1682,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,12 +1697,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1827,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462877</v>
+        <v>124462526</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1843,24 +1842,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -1870,7 +1874,7 @@
         <v>576338</v>
       </c>
       <c r="R12" t="n">
-        <v>7056426</v>
+        <v>7056370</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1906,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1916,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1943,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124461936</v>
+        <v>124467291</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1955,43 +1959,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576362</v>
+        <v>576639</v>
       </c>
       <c r="R13" t="n">
-        <v>7056386</v>
+        <v>7056205</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2023,7 +2018,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2033,7 +2028,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,22 +2043,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124464956</v>
+        <v>124465974</v>
       </c>
       <c r="B14" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2072,38 +2067,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576386</v>
+        <v>576547</v>
       </c>
       <c r="R14" t="n">
-        <v>7056351</v>
+        <v>7056300</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124461847</v>
+        <v>124463988</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,16 +2188,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2208,19 +2208,19 @@
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576357</v>
+        <v>576347</v>
       </c>
       <c r="R15" t="n">
-        <v>7056418</v>
+        <v>7056490</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2262,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2294,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466297</v>
+        <v>124462696</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,21 +2310,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2329,10 +2334,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576620</v>
+        <v>576319</v>
       </c>
       <c r="R16" t="n">
-        <v>7056231</v>
+        <v>7056393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2406,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462807</v>
+        <v>124465046</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,16 +2422,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2437,7 +2442,7 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2446,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576313</v>
+        <v>576421</v>
       </c>
       <c r="R17" t="n">
-        <v>7056397</v>
+        <v>7056365</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2486,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,12 +2496,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2523,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467291</v>
+        <v>124464956</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>96227</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,25 +2535,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2563,10 +2563,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576639</v>
+        <v>576386</v>
       </c>
       <c r="R18" t="n">
-        <v>7056205</v>
+        <v>7056351</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2598,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124465046</v>
+        <v>124466297</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,39 +2651,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576421</v>
+        <v>576620</v>
       </c>
       <c r="R19" t="n">
-        <v>7056365</v>
+        <v>7056231</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2715,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2725,7 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2752,10 +2747,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124463852</v>
+        <v>124462877</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,39 +2763,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576328</v>
+        <v>576338</v>
       </c>
       <c r="R20" t="n">
-        <v>7056469</v>
+        <v>7056426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,12 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2862,22 +2847,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462424</v>
+        <v>124462957</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,16 +2875,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2910,7 +2895,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2919,10 +2904,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576338</v>
+        <v>576305</v>
       </c>
       <c r="R21" t="n">
-        <v>7056370</v>
+        <v>7056419</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2954,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2964,7 +2949,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2979,22 +2969,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462696</v>
+        <v>124461847</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,34 +2997,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576319</v>
+        <v>576357</v>
       </c>
       <c r="R22" t="n">
-        <v>7056393</v>
+        <v>7056418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3066,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3076,7 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3103,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124465974</v>
+        <v>124462807</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,16 +3114,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3144,14 +3139,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576547</v>
+        <v>576313</v>
       </c>
       <c r="R23" t="n">
-        <v>7056300</v>
+        <v>7056397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124463852</v>
+        <v>124465974</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,19 +1502,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576328</v>
+        <v>576547</v>
       </c>
       <c r="R9" t="n">
-        <v>7056469</v>
+        <v>7056300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124461936</v>
+        <v>124467291</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,43 +1599,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576362</v>
+        <v>576639</v>
       </c>
       <c r="R10" t="n">
-        <v>7056386</v>
+        <v>7056205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1672,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1682,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,22 +1683,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464981</v>
+        <v>124462696</v>
       </c>
       <c r="B11" t="n">
-        <v>56112</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,39 +1711,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576414</v>
+        <v>576319</v>
       </c>
       <c r="R11" t="n">
-        <v>7056380</v>
+        <v>7056393</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1789,7 +1770,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1799,7 +1780,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,10 +1807,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462526</v>
+        <v>124462807</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1842,16 +1823,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1862,7 +1843,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1871,10 +1852,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576338</v>
+        <v>576313</v>
       </c>
       <c r="R12" t="n">
-        <v>7056370</v>
+        <v>7056397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1906,7 +1887,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1916,7 +1897,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1931,22 +1917,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124467291</v>
+        <v>124461936</v>
       </c>
       <c r="B13" t="n">
-        <v>91012</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1959,34 +1945,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576639</v>
+        <v>576362</v>
       </c>
       <c r="R13" t="n">
-        <v>7056205</v>
+        <v>7056386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2018,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2028,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2043,22 +2038,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124465974</v>
+        <v>124463988</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,16 +2066,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2091,19 +2086,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576547</v>
+        <v>576347</v>
       </c>
       <c r="R14" t="n">
-        <v>7056300</v>
+        <v>7056490</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2140,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2172,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124463988</v>
+        <v>124464981</v>
       </c>
       <c r="B15" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2188,27 +2188,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576347</v>
+        <v>576414</v>
       </c>
       <c r="R15" t="n">
-        <v>7056490</v>
+        <v>7056380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,12 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2294,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462696</v>
+        <v>124466297</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,21 +2305,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2334,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576319</v>
+        <v>576620</v>
       </c>
       <c r="R16" t="n">
-        <v>7056393</v>
+        <v>7056231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2369,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2406,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124465046</v>
+        <v>124462877</v>
       </c>
       <c r="B17" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2422,39 +2417,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576421</v>
+        <v>576338</v>
       </c>
       <c r="R17" t="n">
-        <v>7056365</v>
+        <v>7056426</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2486,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2496,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,22 +2501,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124464956</v>
+        <v>124461847</v>
       </c>
       <c r="B18" t="n">
-        <v>96227</v>
+        <v>56714</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2535,38 +2525,43 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576386</v>
+        <v>576357</v>
       </c>
       <c r="R18" t="n">
-        <v>7056351</v>
+        <v>7056418</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2593,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2603,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,10 +2630,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124466297</v>
+        <v>124462957</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>57513</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,34 +2646,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576620</v>
+        <v>576305</v>
       </c>
       <c r="R19" t="n">
-        <v>7056231</v>
+        <v>7056419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2747,10 +2752,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462877</v>
+        <v>124462526</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,24 +2768,29 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2790,7 +2800,7 @@
         <v>576338</v>
       </c>
       <c r="R20" t="n">
-        <v>7056426</v>
+        <v>7056370</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2842,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,7 +2869,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462957</v>
+        <v>124463852</v>
       </c>
       <c r="B21" t="n">
         <v>57513</v>
@@ -2895,7 +2905,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2904,10 +2914,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576305</v>
+        <v>576328</v>
       </c>
       <c r="R21" t="n">
-        <v>7056419</v>
+        <v>7056469</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2949,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,12 +2959,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,7 +2991,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124461847</v>
+        <v>124465046</v>
       </c>
       <c r="B22" t="n">
         <v>56714</v>
@@ -3022,14 +3032,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576357</v>
+        <v>576421</v>
       </c>
       <c r="R22" t="n">
-        <v>7056418</v>
+        <v>7056365</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,10 +3108,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462807</v>
+        <v>124464956</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3110,43 +3120,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576313</v>
+        <v>576386</v>
       </c>
       <c r="R23" t="n">
-        <v>7056397</v>
+        <v>7056351</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -2289,10 +2289,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466297</v>
+        <v>124462877</v>
       </c>
       <c r="B16" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,21 +2305,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2329,10 +2329,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576620</v>
+        <v>576338</v>
       </c>
       <c r="R16" t="n">
-        <v>7056231</v>
+        <v>7056426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,22 +2389,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462877</v>
+        <v>124466297</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,21 +2417,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576338</v>
+        <v>576620</v>
       </c>
       <c r="R17" t="n">
-        <v>7056426</v>
+        <v>7056231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,12 +2501,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124465974</v>
+        <v>124463988</v>
       </c>
       <c r="B9" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,16 +1482,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1502,19 +1502,19 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576547</v>
+        <v>576347</v>
       </c>
       <c r="R9" t="n">
-        <v>7056300</v>
+        <v>7056490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467291</v>
+        <v>124463852</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1599,34 +1604,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576639</v>
+        <v>576328</v>
       </c>
       <c r="R10" t="n">
-        <v>7056205</v>
+        <v>7056469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124462696</v>
+        <v>124464956</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,25 +1722,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1735,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576319</v>
+        <v>576386</v>
       </c>
       <c r="R11" t="n">
-        <v>7056393</v>
+        <v>7056351</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1770,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1780,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,10 +1822,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462807</v>
+        <v>124465974</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1823,16 +1838,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1848,14 +1863,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576313</v>
+        <v>576547</v>
       </c>
       <c r="R12" t="n">
-        <v>7056397</v>
+        <v>7056300</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1887,7 +1902,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1897,12 +1912,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1939,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124461936</v>
+        <v>124462807</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,31 +1955,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1978,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576362</v>
+        <v>576313</v>
       </c>
       <c r="R13" t="n">
-        <v>7056386</v>
+        <v>7056397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2019,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2029,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,22 +2049,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124463988</v>
+        <v>124465046</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,16 +2077,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2086,7 +2097,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2095,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576347</v>
+        <v>576421</v>
       </c>
       <c r="R14" t="n">
-        <v>7056490</v>
+        <v>7056365</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,12 +2151,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2289,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462877</v>
+        <v>124462526</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2305,24 +2311,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2332,7 +2343,7 @@
         <v>576338</v>
       </c>
       <c r="R16" t="n">
-        <v>7056426</v>
+        <v>7056370</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2375,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2385,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2412,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466297</v>
+        <v>124461936</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,34 +2428,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576620</v>
+        <v>576362</v>
       </c>
       <c r="R17" t="n">
-        <v>7056231</v>
+        <v>7056386</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2486,7 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2501,22 +2521,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124461847</v>
+        <v>124467291</v>
       </c>
       <c r="B18" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2529,39 +2549,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576357</v>
+        <v>576639</v>
       </c>
       <c r="R18" t="n">
-        <v>7056418</v>
+        <v>7056205</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2593,7 +2608,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2603,7 +2618,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2752,10 +2767,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462526</v>
+        <v>124462877</v>
       </c>
       <c r="B20" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2768,29 +2783,24 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2800,7 +2810,7 @@
         <v>576338</v>
       </c>
       <c r="R20" t="n">
-        <v>7056370</v>
+        <v>7056426</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2832,7 +2842,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2842,7 +2852,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2879,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124463852</v>
+        <v>124461847</v>
       </c>
       <c r="B21" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,16 +2895,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2905,19 +2915,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576328</v>
+        <v>576357</v>
       </c>
       <c r="R21" t="n">
-        <v>7056469</v>
+        <v>7056418</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2949,7 +2959,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2959,12 +2969,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2991,10 +2996,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124465046</v>
+        <v>124462696</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3007,39 +3012,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576421</v>
+        <v>576319</v>
       </c>
       <c r="R22" t="n">
-        <v>7056365</v>
+        <v>7056393</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,10 +3108,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124464956</v>
+        <v>124466297</v>
       </c>
       <c r="B23" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3120,25 +3120,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576386</v>
+        <v>576620</v>
       </c>
       <c r="R23" t="n">
-        <v>7056351</v>
+        <v>7056231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124463988</v>
+        <v>124467291</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,39 +1482,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576347</v>
+        <v>576639</v>
       </c>
       <c r="R9" t="n">
-        <v>7056490</v>
+        <v>7056205</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1541,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1551,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:46</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1578,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124463852</v>
+        <v>124464981</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,27 +1594,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1633,10 +1623,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576328</v>
+        <v>576414</v>
       </c>
       <c r="R10" t="n">
-        <v>7056469</v>
+        <v>7056380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,12 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124464956</v>
+        <v>124465974</v>
       </c>
       <c r="B11" t="n">
-        <v>96227</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1722,38 +1707,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576386</v>
+        <v>576547</v>
       </c>
       <c r="R11" t="n">
-        <v>7056351</v>
+        <v>7056300</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1812,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124465974</v>
+        <v>124462957</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,16 +1828,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1863,14 +1853,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576547</v>
+        <v>576305</v>
       </c>
       <c r="R12" t="n">
-        <v>7056300</v>
+        <v>7056419</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1902,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1912,7 +1902,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,10 +1934,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462807</v>
+        <v>124464956</v>
       </c>
       <c r="B13" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1951,43 +1946,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576313</v>
+        <v>576386</v>
       </c>
       <c r="R13" t="n">
-        <v>7056397</v>
+        <v>7056351</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,7 +2009,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2029,12 +2019,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2046,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124465046</v>
+        <v>124461847</v>
       </c>
       <c r="B14" t="n">
         <v>56714</v>
@@ -2102,14 +2087,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576421</v>
+        <v>576357</v>
       </c>
       <c r="R14" t="n">
-        <v>7056365</v>
+        <v>7056418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2126,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,7 +2136,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2163,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124464981</v>
+        <v>124462526</v>
       </c>
       <c r="B15" t="n">
-        <v>56112</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,21 +2179,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2223,10 +2208,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576414</v>
+        <v>576338</v>
       </c>
       <c r="R15" t="n">
-        <v>7056380</v>
+        <v>7056370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2258,7 +2243,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2268,7 +2253,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2283,22 +2268,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462526</v>
+        <v>124462877</v>
       </c>
       <c r="B16" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,29 +2296,24 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
@@ -2343,7 +2323,7 @@
         <v>576338</v>
       </c>
       <c r="R16" t="n">
-        <v>7056370</v>
+        <v>7056426</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2375,7 +2355,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,7 +2365,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,10 +2392,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124461936</v>
+        <v>124466297</v>
       </c>
       <c r="B17" t="n">
-        <v>57666</v>
+        <v>91030</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2428,43 +2408,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576362</v>
+        <v>576620</v>
       </c>
       <c r="R17" t="n">
-        <v>7056386</v>
+        <v>7056231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2467,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2506,7 +2477,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,22 +2492,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124467291</v>
+        <v>124462807</v>
       </c>
       <c r="B18" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2549,34 +2520,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576639</v>
+        <v>576313</v>
       </c>
       <c r="R18" t="n">
-        <v>7056205</v>
+        <v>7056397</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2608,7 +2584,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2618,7 +2594,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2645,7 +2626,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462957</v>
+        <v>124463852</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2681,7 +2662,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2690,10 +2671,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576305</v>
+        <v>576328</v>
       </c>
       <c r="R19" t="n">
-        <v>7056419</v>
+        <v>7056469</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2725,7 +2706,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2735,12 +2716,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,7 +2748,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462877</v>
+        <v>124462696</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2807,10 +2788,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576338</v>
+        <v>576319</v>
       </c>
       <c r="R20" t="n">
-        <v>7056426</v>
+        <v>7056393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2842,7 +2823,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2852,7 +2833,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2867,19 +2848,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461847</v>
+        <v>124465046</v>
       </c>
       <c r="B21" t="n">
         <v>56714</v>
@@ -2920,14 +2901,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576357</v>
+        <v>576421</v>
       </c>
       <c r="R21" t="n">
-        <v>7056418</v>
+        <v>7056365</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2959,7 +2940,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2969,7 +2950,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,10 +2977,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462696</v>
+        <v>124463988</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,34 +2993,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576319</v>
+        <v>576347</v>
       </c>
       <c r="R22" t="n">
-        <v>7056393</v>
+        <v>7056490</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3071,7 +3057,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3081,7 +3067,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3108,10 +3099,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466297</v>
+        <v>124461936</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3124,34 +3115,43 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576620</v>
+        <v>576362</v>
       </c>
       <c r="R23" t="n">
-        <v>7056231</v>
+        <v>7056386</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124467291</v>
+        <v>124462807</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,34 +1482,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576639</v>
+        <v>576313</v>
       </c>
       <c r="R9" t="n">
-        <v>7056205</v>
+        <v>7056397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1541,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1551,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1578,10 +1588,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124464981</v>
+        <v>124467291</v>
       </c>
       <c r="B10" t="n">
-        <v>56112</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1594,39 +1604,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576414</v>
+        <v>576639</v>
       </c>
       <c r="R10" t="n">
-        <v>7056380</v>
+        <v>7056205</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1673,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1700,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124465974</v>
+        <v>124462877</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,39 +1716,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576547</v>
+        <v>576338</v>
       </c>
       <c r="R11" t="n">
-        <v>7056300</v>
+        <v>7056426</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,22 +1800,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124462957</v>
+        <v>124461936</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,27 +1828,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1857,10 +1861,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576305</v>
+        <v>576362</v>
       </c>
       <c r="R12" t="n">
-        <v>7056419</v>
+        <v>7056386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,12 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,22 +1921,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124464956</v>
+        <v>124465046</v>
       </c>
       <c r="B13" t="n">
-        <v>96227</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1946,38 +1945,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576386</v>
+        <v>576421</v>
       </c>
       <c r="R13" t="n">
-        <v>7056351</v>
+        <v>7056365</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2009,7 +2013,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2019,7 +2023,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2046,7 +2050,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124461847</v>
+        <v>124462424</v>
       </c>
       <c r="B14" t="n">
         <v>56714</v>
@@ -2087,14 +2091,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576357</v>
+        <v>576338</v>
       </c>
       <c r="R14" t="n">
-        <v>7056418</v>
+        <v>7056370</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2126,7 +2130,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2136,7 +2140,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,22 +2155,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462526</v>
+        <v>124462696</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2179,39 +2183,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576338</v>
+        <v>576319</v>
       </c>
       <c r="R15" t="n">
-        <v>7056370</v>
+        <v>7056393</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2243,7 +2242,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2253,7 +2252,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,22 +2267,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124462877</v>
+        <v>124465974</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2296,34 +2295,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576338</v>
+        <v>576547</v>
       </c>
       <c r="R16" t="n">
-        <v>7056426</v>
+        <v>7056300</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2355,7 +2359,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2365,7 +2369,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,22 +2384,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466297</v>
+        <v>124464956</v>
       </c>
       <c r="B17" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2404,25 +2408,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2432,10 +2436,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576620</v>
+        <v>576386</v>
       </c>
       <c r="R17" t="n">
-        <v>7056231</v>
+        <v>7056351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2467,7 +2471,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2477,7 +2481,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2504,10 +2508,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124462807</v>
+        <v>124466297</v>
       </c>
       <c r="B18" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2520,39 +2524,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576313</v>
+        <v>576620</v>
       </c>
       <c r="R18" t="n">
-        <v>7056397</v>
+        <v>7056231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2584,7 +2583,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2594,12 +2593,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2626,7 +2620,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124463852</v>
+        <v>124462957</v>
       </c>
       <c r="B19" t="n">
         <v>57513</v>
@@ -2662,7 +2656,7 @@
       <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2671,10 +2665,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576328</v>
+        <v>576305</v>
       </c>
       <c r="R19" t="n">
-        <v>7056469</v>
+        <v>7056419</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2706,7 +2700,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2716,12 +2710,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,10 +2742,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124462696</v>
+        <v>124464981</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>56112</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2764,34 +2758,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576319</v>
+        <v>576414</v>
       </c>
       <c r="R20" t="n">
-        <v>7056393</v>
+        <v>7056380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2823,7 +2822,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2833,7 +2832,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,7 +2859,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124465046</v>
+        <v>124461847</v>
       </c>
       <c r="B21" t="n">
         <v>56714</v>
@@ -2901,14 +2900,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576421</v>
+        <v>576357</v>
       </c>
       <c r="R21" t="n">
-        <v>7056365</v>
+        <v>7056418</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2940,7 +2939,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2950,7 +2949,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2977,7 +2976,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124463988</v>
+        <v>124463852</v>
       </c>
       <c r="B22" t="n">
         <v>57513</v>
@@ -3022,10 +3021,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576347</v>
+        <v>576328</v>
       </c>
       <c r="R22" t="n">
-        <v>7056490</v>
+        <v>7056469</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3057,7 +3056,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3067,7 +3066,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3099,10 +3098,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124461936</v>
+        <v>124463988</v>
       </c>
       <c r="B23" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3115,31 +3114,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3148,10 +3143,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576362</v>
+        <v>576347</v>
       </c>
       <c r="R23" t="n">
-        <v>7056386</v>
+        <v>7056490</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3183,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3193,7 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,12 +3208,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124462807</v>
+        <v>124464981</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,27 +1482,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576313</v>
+        <v>576414</v>
       </c>
       <c r="R9" t="n">
-        <v>7056397</v>
+        <v>7056380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,12 +1556,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1588,10 +1583,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124467291</v>
+        <v>124463988</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,34 +1599,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576639</v>
+        <v>576347</v>
       </c>
       <c r="R10" t="n">
-        <v>7056205</v>
+        <v>7056490</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,7 +1673,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124462877</v>
+        <v>124465046</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,34 +1721,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576338</v>
+        <v>576421</v>
       </c>
       <c r="R11" t="n">
-        <v>7056426</v>
+        <v>7056365</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1775,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1785,7 +1795,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,22 +1810,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124461936</v>
+        <v>124467291</v>
       </c>
       <c r="B12" t="n">
-        <v>57666</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,43 +1838,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576362</v>
+        <v>576639</v>
       </c>
       <c r="R12" t="n">
-        <v>7056386</v>
+        <v>7056205</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1897,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1907,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,22 +1922,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124465046</v>
+        <v>124465974</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,16 +1950,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1969,19 +1970,19 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576421</v>
+        <v>576547</v>
       </c>
       <c r="R13" t="n">
-        <v>7056365</v>
+        <v>7056300</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2013,7 +2014,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2023,7 +2024,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2050,10 +2051,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124462424</v>
+        <v>124461936</v>
       </c>
       <c r="B14" t="n">
-        <v>56714</v>
+        <v>57666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2066,27 +2067,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2095,10 +2100,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576338</v>
+        <v>576362</v>
       </c>
       <c r="R14" t="n">
-        <v>7056370</v>
+        <v>7056386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2130,7 +2135,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2140,7 +2145,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2167,10 +2172,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462696</v>
+        <v>124462424</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2183,34 +2188,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>576319</v>
+        <v>576338</v>
       </c>
       <c r="R15" t="n">
-        <v>7056393</v>
+        <v>7056370</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2242,7 +2252,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2252,7 +2262,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,22 +2277,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124465974</v>
+        <v>124464956</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>96227</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2291,43 +2301,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576547</v>
+        <v>576386</v>
       </c>
       <c r="R16" t="n">
-        <v>7056300</v>
+        <v>7056351</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2359,7 +2364,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2369,7 +2374,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2396,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464956</v>
+        <v>124462807</v>
       </c>
       <c r="B17" t="n">
-        <v>96227</v>
+        <v>57513</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2408,38 +2413,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576386</v>
+        <v>576313</v>
       </c>
       <c r="R17" t="n">
-        <v>7056351</v>
+        <v>7056397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2471,7 +2481,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2481,7 +2491,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2620,10 +2635,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462957</v>
+        <v>124462877</v>
       </c>
       <c r="B19" t="n">
-        <v>57513</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2636,39 +2651,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576305</v>
+        <v>576338</v>
       </c>
       <c r="R19" t="n">
-        <v>7056419</v>
+        <v>7056426</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2700,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2710,12 +2720,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2730,22 +2735,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464981</v>
+        <v>124463852</v>
       </c>
       <c r="B20" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2758,27 +2763,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2787,10 +2792,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576414</v>
+        <v>576328</v>
       </c>
       <c r="R20" t="n">
-        <v>7056380</v>
+        <v>7056469</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2822,7 +2827,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2832,7 +2837,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2859,10 +2869,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124461847</v>
+        <v>124462696</v>
       </c>
       <c r="B21" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2875,39 +2885,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576357</v>
+        <v>576319</v>
       </c>
       <c r="R21" t="n">
-        <v>7056418</v>
+        <v>7056393</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2939,7 +2944,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2949,7 +2954,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2976,10 +2981,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124463852</v>
+        <v>124461847</v>
       </c>
       <c r="B22" t="n">
-        <v>57513</v>
+        <v>56714</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2992,16 +2997,16 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3012,19 +3017,19 @@
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576328</v>
+        <v>576357</v>
       </c>
       <c r="R22" t="n">
-        <v>7056469</v>
+        <v>7056418</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3056,7 +3061,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3066,12 +3071,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3098,7 +3098,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124463988</v>
+        <v>124462957</v>
       </c>
       <c r="B23" t="n">
         <v>57513</v>
@@ -3134,7 +3134,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576347</v>
+        <v>576305</v>
       </c>
       <c r="R23" t="n">
-        <v>7056490</v>
+        <v>7056419</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3178,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -1466,10 +1466,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124464981</v>
+        <v>124463988</v>
       </c>
       <c r="B9" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1482,27 +1482,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1511,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576414</v>
+        <v>576347</v>
       </c>
       <c r="R9" t="n">
-        <v>7056380</v>
+        <v>7056490</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1556,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1583,7 +1588,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124463988</v>
+        <v>124462957</v>
       </c>
       <c r="B10" t="n">
         <v>57513</v>
@@ -1619,7 +1624,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1628,10 +1633,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576347</v>
+        <v>576305</v>
       </c>
       <c r="R10" t="n">
-        <v>7056490</v>
+        <v>7056419</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1663,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1673,12 +1678,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack på gran</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124465046</v>
+        <v>124462807</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,16 +1726,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1741,7 +1746,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576421</v>
+        <v>576313</v>
       </c>
       <c r="R11" t="n">
-        <v>7056365</v>
+        <v>7056397</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1785,7 +1790,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1795,7 +1800,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,10 +1832,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124467291</v>
+        <v>124465046</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,34 +1848,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576639</v>
+        <v>576421</v>
       </c>
       <c r="R12" t="n">
-        <v>7056205</v>
+        <v>7056365</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1897,7 +1912,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1907,7 +1922,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:58</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,10 +1949,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124465974</v>
+        <v>124462696</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1950,39 +1965,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576547</v>
+        <v>576319</v>
       </c>
       <c r="R13" t="n">
-        <v>7056300</v>
+        <v>7056393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2014,7 +2024,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,7 +2034,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2051,10 +2061,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124461936</v>
+        <v>124463852</v>
       </c>
       <c r="B14" t="n">
-        <v>57666</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2067,31 +2077,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2100,10 +2106,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576362</v>
+        <v>576328</v>
       </c>
       <c r="R14" t="n">
-        <v>7056386</v>
+        <v>7056469</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2141,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2145,7 +2151,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,19 +2171,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462424</v>
+        <v>124462526</v>
       </c>
       <c r="B15" t="n">
         <v>56714</v>
@@ -2252,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2262,7 +2273,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2289,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124464956</v>
+        <v>124461936</v>
       </c>
       <c r="B16" t="n">
-        <v>96227</v>
+        <v>57666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2301,38 +2312,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576386</v>
+        <v>576362</v>
       </c>
       <c r="R16" t="n">
-        <v>7056351</v>
+        <v>7056386</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2364,7 +2384,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2374,7 +2394,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,22 +2409,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124462807</v>
+        <v>124464956</v>
       </c>
       <c r="B17" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,43 +2433,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576313</v>
+        <v>576386</v>
       </c>
       <c r="R17" t="n">
-        <v>7056397</v>
+        <v>7056351</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2481,7 +2496,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2491,12 +2506,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2523,10 +2533,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124466297</v>
+        <v>124465974</v>
       </c>
       <c r="B18" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2539,34 +2549,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576620</v>
+        <v>576547</v>
       </c>
       <c r="R18" t="n">
-        <v>7056231</v>
+        <v>7056300</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2598,7 +2613,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2608,7 +2623,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2635,10 +2650,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124462877</v>
+        <v>124461847</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2651,34 +2666,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576338</v>
+        <v>576357</v>
       </c>
       <c r="R19" t="n">
-        <v>7056426</v>
+        <v>7056418</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2710,7 +2730,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,7 +2740,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2735,22 +2755,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124463852</v>
+        <v>124464981</v>
       </c>
       <c r="B20" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2763,27 +2783,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2792,10 +2812,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576328</v>
+        <v>576414</v>
       </c>
       <c r="R20" t="n">
-        <v>7056469</v>
+        <v>7056380</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2827,7 +2847,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2837,12 +2857,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2869,10 +2884,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124462696</v>
+        <v>124467291</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2885,21 +2900,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2909,10 +2924,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576319</v>
+        <v>576639</v>
       </c>
       <c r="R21" t="n">
-        <v>7056393</v>
+        <v>7056205</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2944,7 +2959,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2954,7 +2969,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2981,10 +2996,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124461847</v>
+        <v>124462877</v>
       </c>
       <c r="B22" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,39 +3012,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576357</v>
+        <v>576338</v>
       </c>
       <c r="R22" t="n">
-        <v>7056418</v>
+        <v>7056426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3061,7 +3071,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3071,7 +3081,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3086,22 +3096,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124462957</v>
+        <v>124466297</v>
       </c>
       <c r="B23" t="n">
-        <v>57513</v>
+        <v>91030</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3114,39 +3124,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576305</v>
+        <v>576620</v>
       </c>
       <c r="R23" t="n">
-        <v>7056419</v>
+        <v>7056231</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3178,7 +3183,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3188,12 +3193,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:25</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,54 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104337157</v>
+        <v>124467291</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576592.536864906</v>
+        <v>576639</v>
       </c>
       <c r="R2" t="n">
-        <v>7056175.377348462</v>
+        <v>7056205</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,54 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104337394</v>
+        <v>124464956</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576639.9522019669</v>
+        <v>576386</v>
       </c>
       <c r="R3" t="n">
-        <v>7056222.341101539</v>
+        <v>7056351</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -859,22 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,54 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104338624</v>
+        <v>124462696</v>
       </c>
       <c r="B4" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576361.820191047</v>
+        <v>576319</v>
       </c>
       <c r="R4" t="n">
-        <v>7056396.664948627</v>
+        <v>7056393</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -972,22 +954,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,27 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104336377</v>
+        <v>124462877</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1030,38 +1007,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576645.9284997425</v>
+        <v>576338</v>
       </c>
       <c r="R5" t="n">
-        <v>7056196.240826938</v>
+        <v>7056426</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1085,22 +1061,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,44 +1091,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104335786</v>
+        <v>124464648</v>
       </c>
       <c r="B6" t="n">
-        <v>77507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1161,20 +1132,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576665.932630884</v>
+        <v>576388</v>
       </c>
       <c r="R6" t="n">
-        <v>7056216.297164583</v>
+        <v>7056426</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,22 +1168,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,54 +1210,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104337416</v>
+        <v>124465974</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576589.2350312177</v>
+        <v>576547</v>
       </c>
       <c r="R7" t="n">
-        <v>7056256.700720191</v>
+        <v>7056300</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1311,22 +1280,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-27</t>
+          <t>2025-04-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,12 +1310,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jonatan Nordström</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1356,12 +1325,7 @@
         <v>104335863</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1394,10 +1358,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576659.3155783322</v>
+        <v>576659</v>
       </c>
       <c r="R8" t="n">
-        <v>7056195.230161706</v>
+        <v>7056195</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,19 +1391,9 @@
           <t>2022-10-27</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-10-27</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,15 +1420,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124463988</v>
+        <v>124462807</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1502,7 +1451,7 @@
       <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1511,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576347</v>
+        <v>576313</v>
       </c>
       <c r="R9" t="n">
-        <v>7056490</v>
+        <v>7056397</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1546,7 +1495,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1556,7 +1505,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1591,12 +1540,7 @@
         <v>124462957</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1710,15 +1654,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124462807</v>
+        <v>124463852</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1746,7 +1685,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1755,10 +1694,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576313</v>
+        <v>576328</v>
       </c>
       <c r="R11" t="n">
-        <v>7056397</v>
+        <v>7056469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1790,7 +1729,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1800,7 +1739,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1832,15 +1771,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124465046</v>
+        <v>124463988</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,16 +1782,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1868,7 +1802,7 @@
       <c r="I12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1877,10 +1811,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576421</v>
+        <v>576347</v>
       </c>
       <c r="R12" t="n">
-        <v>7056365</v>
+        <v>7056490</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1912,7 +1846,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1922,7 +1856,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,53 +1888,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124462696</v>
+        <v>104338624</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576319</v>
+        <v>576362</v>
       </c>
       <c r="R13" t="n">
-        <v>7056393</v>
+        <v>7056396</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2019,22 +1954,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2049,44 +1984,39 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124463852</v>
+        <v>124461847</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2097,19 +2027,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576328</v>
+        <v>576357</v>
       </c>
       <c r="R14" t="n">
-        <v>7056469</v>
+        <v>7056418</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2141,7 +2071,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2151,12 +2081,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:44</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,19 +2108,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124462526</v>
+        <v>124462424</v>
       </c>
       <c r="B15" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2263,7 +2183,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,7 +2193,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,47 +2220,38 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124461936</v>
+        <v>124465046</v>
       </c>
       <c r="B16" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2349,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576362</v>
+        <v>576421</v>
       </c>
       <c r="R16" t="n">
-        <v>7056386</v>
+        <v>7056365</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2384,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2394,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,62 +2320,66 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124464956</v>
+        <v>124461936</v>
       </c>
       <c r="B17" t="n">
-        <v>96227</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576386</v>
+        <v>576362</v>
       </c>
       <c r="R17" t="n">
-        <v>7056351</v>
+        <v>7056386</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2496,7 +2411,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2506,7 +2421,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2521,27 +2436,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Lucas Canales</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124465974</v>
+        <v>124464981</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56522</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,39 +2459,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Arksjön, Arksjön, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576547</v>
+        <v>576414</v>
       </c>
       <c r="R18" t="n">
-        <v>7056300</v>
+        <v>7056380</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2613,7 +2523,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2623,7 +2533,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,58 +2560,49 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124461847</v>
+        <v>104336377</v>
       </c>
       <c r="B19" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>576357</v>
+        <v>576646</v>
       </c>
       <c r="R19" t="n">
-        <v>7056418</v>
+        <v>7056196</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2725,22 +2626,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2767,58 +2658,49 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124464981</v>
+        <v>104336382</v>
       </c>
       <c r="B20" t="n">
-        <v>56112</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206004</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>576414</v>
+        <v>576645</v>
       </c>
       <c r="R20" t="n">
-        <v>7056380</v>
+        <v>7056176</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2842,22 +2724,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2872,65 +2754,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124467291</v>
+        <v>104337157</v>
       </c>
       <c r="B21" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>576639</v>
+        <v>576593</v>
       </c>
       <c r="R21" t="n">
-        <v>7056205</v>
+        <v>7056175</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2954,22 +2832,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>17:58</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>17:58</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2996,53 +2864,49 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124462877</v>
+        <v>104337394</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>576338</v>
+        <v>576640</v>
       </c>
       <c r="R22" t="n">
-        <v>7056426</v>
+        <v>7056222</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3066,22 +2930,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3096,65 +2950,61 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Lucas Canales</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124466297</v>
+        <v>104337416</v>
       </c>
       <c r="B23" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Arksjön, Arksjön, Ång</t>
+          <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>576620</v>
+        <v>576590</v>
       </c>
       <c r="R23" t="n">
-        <v>7056231</v>
+        <v>7056256</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3178,22 +3028,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:48</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3208,15 +3048,211 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Jonatan Nordström</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104335786</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>576665</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7056216</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104335887</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>576668</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7056193</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-10-27</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18009-2022 artfynd.xlsx
+++ b/artfynd/A 18009-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124467291</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464956</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462696</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464648</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465974</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1417,6 +1452,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335863</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462807</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1651,6 +1696,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462957</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1768,6 +1818,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463852</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1885,6 +1940,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124463988</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1993,6 +2053,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104338624</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124461847</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2217,6 +2287,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124462424</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2329,6 +2404,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124465046</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2445,6 +2525,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124461936</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2557,6 +2642,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124464981</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2655,6 +2745,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104336377</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2763,6 +2858,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104336382</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2861,6 +2961,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104337157</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,6 +3064,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104337394</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3057,6 +3167,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104337416</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3155,6 +3270,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335786</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3253,8 +3373,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104335887</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>